--- a/示例配置/合并汇总表_示范校区.xlsx
+++ b/示例配置/合并汇总表_示范校区.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB16"/>
+  <dimension ref="A1:BC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,7 @@
     <col width="14" customWidth="1" min="52" max="52"/>
     <col width="14" customWidth="1" min="53" max="53"/>
     <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="14" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -628,175 +629,180 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>顾问侧续费历史</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>学校名称</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成绩水平</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>性格特点</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>兴趣偏好</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>课堂表现</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>同伴关系</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>已报名课程</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>在读课程</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>学习时长</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>作品成果</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>续费历史</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>入学时间</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>在读时长</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>等级考</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>白名单比赛</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>老师侧支付力</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>家长关注度</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>家长新期待</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>老师复盘</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>学员细节备注</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>家庭背景(老师补充)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>冲突标注</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>学校层次(科技特色)</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>科技特色详情</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>小区房价段</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>住户画像</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>周边竞品</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>家庭消费力</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>推荐话术素材</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>支付力</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>续费风险</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>转介绍潜力</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>跟进优先级</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>推荐产品方向</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>学情画像</t>
         </is>
@@ -900,102 +906,106 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>无续费记录</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>翠湖实验小学</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>中等偏上</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>活泼</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>乐高、编程</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Python入门</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>8个月</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>做过2个小游戏</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>续费1次</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1年9个月</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>机器人1级</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>群内回复:快|进班:偶尔进|疲态:无</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>希望孩子多参加比赛锻炼自信</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>学生技术基础扎实，建议引导参加白名单比赛提升自信心，同时向家长介绍竞赛路线。</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>续费时妈妈犹豫很久，最后奶奶帮忙付；妈妈想推但爸爸不太上心；做项目特别专注但不敢上台展示</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>妈妈全职带娃，对孩子的科技特长比较重视</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
@@ -1009,6 +1019,7 @@
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1104,110 +1115,114 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>续费1次，Scratch→Python</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>阳光重点小学</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>内向</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>画画、阅读</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Python入门</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>AI编程进阶营</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>12个月</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>参加过区级编程比赛获三等奖</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>续费2次</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2年3个月</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Python2级</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>蓝桥杯青少年组2025</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>研学</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>希望冲信奥省赛</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>学生竞赛潜力突出，建议加码竞赛冲刺班，同时关注信奥启蒙衔接，家长配合度高。</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>[老师补充] 性格内向但做项目很有想法，适合推竞赛方向 | 家长非常重视竞赛方向，主动问过信奥路线</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>爸爸IT行业，对竞赛路线了解深入，家庭支持力度大</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
@@ -1221,6 +1236,7 @@
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1320,93 +1336,97 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>新客户，暂无续费</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>老城小学</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>活泼</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>机器人、足球</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>容易走神</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>2个月</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>做过1个小动画</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>未续费</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>2个月</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>未考</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr">
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>群内回复:慢|进班:不进|疲态:轻度</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>新生兴趣点在机器人，但专注力待提升，建议用项目制吸引注意力，家长参与度需提高。</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>[老师补充] 上课容易走神但动手能力强 | 不太清楚家里细节，只知道爸爸在工厂</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
@@ -1421,6 +1441,7 @@
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1520,106 +1541,110 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>无续费记录</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>科技实验小学</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>文静</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>编程、机器人</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Python入门</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>10个月</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>做过3个作品，参加机器人比赛获二等奖</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>续费1次</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>2024-08</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1年10个月</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>机器人3级</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>全国青少年机器人竞赛2025</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>希望冲全国赛</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>竞赛型选手，建议重点培养，加码竞赛冲刺班，同时关注心理素质训练。</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>妈妈是校区志愿者，经常帮忙宣传，转介绍潜力很大</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>妈妈是校区志愿者，家庭对竞赛非常支持</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
@@ -1633,6 +1658,7 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1728,110 +1754,114 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>续费3次，Scratch→Python→竞赛班</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>实验中学附小</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>沉稳</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>编程、数学</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Python入门</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>竞赛冲刺班</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>18个月</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>参加信息学奥赛获省赛一等奖</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>续费3次</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>2年9个月</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Python2级</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>信息学奥赛CSP-J 2025、蓝桥杯2025</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>研学、lab</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>冲CSP-S提高组</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>顶尖竞赛选手，建议全力备战CSP-S，同时关注小升初衔接，家长全力支持。</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>家长是校区志愿者，经常帮忙宣传</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>爸爸IT行业高级工程师，对孩子编程培养有清晰规划</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
@@ -1845,6 +1875,7 @@
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1944,102 +1975,106 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>新客户，暂无续费</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>金域小学</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>开朗</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>机器人、篮球</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>积极主动</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>机器人编程</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>4个月</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>做过2个机器人项目</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>未续费</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>4个月</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>机器人1级</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr">
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>群内回复:快|进班:偶尔进|疲态:无</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>希望孩子学有所成</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>学生兴趣浓厚表现积极，建议引导参加机器人等级考和白名单比赛，提升成就感。</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>同事介绍的，信任度较高</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>妈妈是公务员，比较重视素质教育</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
@@ -2053,6 +2088,7 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2148,98 +2184,102 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>无续费记录</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>保利小学</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>中等偏上</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>文静</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>画画、拼图</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2个月</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>做过1个动画故事</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>未续费</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>2个月</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>未考</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr">
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>群内回复:快|进班:偶尔进|疲态:无</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>希望培养孩子创造力</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>低龄新生，创意表达能力强，适合继续Scratch路线，后续可衔接Python入门。</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>妈妈是老师，教育理念好，配合度高</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
@@ -2253,6 +2293,7 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2352,94 +2393,98 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>无续费记录</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>老城二小</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>调皮</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>游戏、机器人</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>稳定踏实</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>机器人编程</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>5个月</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>做过2个小游戏</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>未续费</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>5个月</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>机器人1级</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr">
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>群内回复:慢|进班:不进|疲态:无</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
         <is>
           <t>学生动手能力不错但家长参与度低，建议加强家校沟通，引导家长关注孩子进步。</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr">
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>奶奶日常带，父母工作忙较少关注</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
@@ -2453,6 +2498,7 @@
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2552,106 +2598,110 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>续费1次，Scratch→机器人</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>华润小学</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>认真</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>机器人、画画</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>机器人编程</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>6个月</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>做过3个机器人作品，参加区级比赛获优秀奖</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>续费1次</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>9个月</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>机器人2级</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>VEX</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>希望走机器人竞赛路线</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>学生潜力好，建议加码机器人等级考+VEX竞赛路线，家长支持力度大。</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>妈妈很关注孩子考级进度</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>妈妈是律师，对孩子的竞赛规划很清晰</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
@@ -2665,6 +2715,7 @@
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2760,106 +2811,110 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>续费2次，Scratch→AI编程营</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>星河湾国际学校</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>编程、演讲</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>积极主动</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>AI编程进阶营</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>竞赛冲刺班</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>14个月</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>参加过AI创新赛获市级一等奖</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>续费2次</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>1年3个月</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Python2级</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>全国青少年AI创新赛2026</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>研学、lab</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>希望冲国赛</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>高潜力竞赛选手，表达+技术双优，建议全力备战国赛，同时关注研学拓展。</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr">
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>爸爸企业高管，对孩子培养投入大，视野开阔</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
@@ -2873,6 +2928,7 @@
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2968,106 +3024,110 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>续费2次，Python→竞赛班</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>学府小学</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>沉稳</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>编程、数学、科学</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>竞赛冲刺班</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>信奥启蒙班</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>20个月</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>参加信息学奥赛获省赛一等奖、蓝桥杯国赛一等奖</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>续费3次</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>2年9个月</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>Python2级</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>CSP-J 2025、CSP-S 2025、蓝桥杯2025</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>研学、lab、VEX</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>冲NOI</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>顶尖信奥选手，建议全力冲CSP-S一等奖+NOI，同时关注小升初特长生路线。</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr">
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr">
         <is>
           <t>爸爸大学教授，学术家庭，对孩子培养规划清晰长远</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
@@ -3081,6 +3141,7 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3180,98 +3241,102 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>新客户，暂无续费</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>龙湖小学</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>活泼</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>画画、唱歌</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>容易走神</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1个月</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>做过1个小动画</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>未续费</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>1个月</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>未考</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr">
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr">
         <is>
           <t>群内回复:快|进班:偶尔进|疲态:无</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>希望培养孩子专注力</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>低龄新生，兴趣点在画画，建议用Scratch创意画吸引注意力，逐步提升专注力。</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>妈妈是设计师，对孩子的创意表达比较支持</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
@@ -3285,6 +3350,7 @@
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3384,98 +3450,102 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>无续费记录</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>中航城小学</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>中等偏上</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>理性</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>编程、围棋</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>稳定踏实</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Python入门</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>7个月</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>做过2个Python小程序</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>续费1次</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>8个月</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>Python1级</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr">
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr">
         <is>
           <t>群内回复:快|进班:偶尔进|疲态:无</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>希望孩子考级</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>学生逻辑思维好，适合Python路线，建议推进Python等级考，长期培养。</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr">
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr">
         <is>
           <t>爸爸工程师，比较理性，注重逻辑思维培养</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
@@ -3489,6 +3559,7 @@
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3588,94 +3659,98 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>新客户，暂无续费</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>社区小学</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>活泼</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>足球、游戏</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>容易走神</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Scratch基础</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>3个月</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>做过1个小游戏</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>未续费</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>3个月</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>未考</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr">
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
         <is>
           <t>群内回复:慢|进班:不进|疲态:轻度</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr">
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr">
         <is>
           <t>学生兴趣在游戏类项目，建议用游戏化教学吸引注意力，家长参与度需提升。</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr">
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr">
         <is>
           <t>妈妈护士工作忙，日常老人带，关注度偏低</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
@@ -3689,6 +3764,7 @@
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3784,106 +3860,110 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>续费1次，Scratch→Python</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>融创小学</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>前几名</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>认真</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>编程、数学</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Python入门</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>AI编程进阶营</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>10个月</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>做过3个Python项目，参加编程比赛获区级二等奖</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>续费1次</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>11个月</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>Python2级</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>蓝桥杯青少年组2026</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>研学</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>群内回复:快|进班:经常进|疲态:无</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>希望冲省赛</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>学生竞赛潜力好，建议加码竞赛冲刺班，家长配合度高，研学路线可同步推进。</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr">
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr">
         <is>
           <t>爸爸金融行业，教育投入意愿强，对竞赛方向支持</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
@@ -3897,9 +3977,10 @@
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AW2:AW16">
+  <conditionalFormatting sqref="AX2:AX16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"高"</formula>
     </cfRule>
@@ -3910,7 +3991,7 @@
       <formula>"低"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AX2:AX16">
+  <conditionalFormatting sqref="AY2:AY16">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"高"</formula>
     </cfRule>
@@ -3921,7 +4002,7 @@
       <formula>"低"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY2:AY16">
+  <conditionalFormatting sqref="AZ2:AZ16">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"高"</formula>
     </cfRule>
